--- a/AAII_Financials/Yearly/BUSE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BUSE_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>BUSE</t>
   </si>
@@ -732,7 +732,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>666800</v>
+        <v>716500</v>
       </c>
       <c r="E8" s="3">
         <v>454800</v>
@@ -834,7 +834,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>666800</v>
+        <v>716500</v>
       </c>
       <c r="E10" s="3">
         <v>454800</v>
@@ -1007,14 +1007,14 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>104300</v>
+      </c>
+      <c r="E14" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F14" s="3">
+        <v>4300</v>
       </c>
       <c r="G14" s="3">
         <v>4200</v>
@@ -1128,13 +1128,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>453200</v>
+        <v>398500</v>
       </c>
       <c r="E17" s="3">
-        <v>285800</v>
+        <v>277700</v>
       </c>
       <c r="F17" s="3">
-        <v>269000</v>
+        <v>264700</v>
       </c>
       <c r="G17" s="3">
         <v>264000</v>
@@ -1179,13 +1179,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>213700</v>
+        <v>317900</v>
       </c>
       <c r="E18" s="3">
-        <v>169000</v>
+        <v>177100</v>
       </c>
       <c r="F18" s="3">
-        <v>170000</v>
+        <v>174300</v>
       </c>
       <c r="G18" s="3">
         <v>181600</v>
@@ -1302,13 +1302,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>216800</v>
+        <v>321100</v>
       </c>
       <c r="E21" s="3">
-        <v>173900</v>
+        <v>182000</v>
       </c>
       <c r="F21" s="3">
-        <v>185600</v>
+        <v>189900</v>
       </c>
       <c r="G21" s="3">
         <v>197900</v>
